--- a/artfynd/A 59526-2025 artfynd.xlsx
+++ b/artfynd/A 59526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688132</v>
       </c>
       <c r="B2" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59526-2025 artfynd.xlsx
+++ b/artfynd/A 59526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688132</v>
       </c>
       <c r="B2" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59526-2025 artfynd.xlsx
+++ b/artfynd/A 59526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688132</v>
       </c>
       <c r="B2" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59526-2025 artfynd.xlsx
+++ b/artfynd/A 59526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688132</v>
       </c>
       <c r="B2" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59526-2025 artfynd.xlsx
+++ b/artfynd/A 59526-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>130162528</v>
       </c>
       <c r="B3" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>130162427</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59526-2025 artfynd.xlsx
+++ b/artfynd/A 59526-2025 artfynd.xlsx
@@ -781,27 +781,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130162528</v>
+        <v>130162427</v>
       </c>
       <c r="B3" t="n">
-        <v>58198</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -812,7 +812,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495666</v>
+        <v>495670</v>
       </c>
       <c r="R3" t="n">
-        <v>6601249</v>
+        <v>6601198</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +866,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hack i död gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,6 +886,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -898,27 +923,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130162427</v>
+        <v>130162528</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>58224</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -929,7 +954,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -938,13 +963,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495670</v>
+        <v>495666</v>
       </c>
       <c r="R4" t="n">
-        <v>6601198</v>
+        <v>6601249</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,12 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hack i död gran</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,26 +1023,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 59526-2025 artfynd.xlsx
+++ b/artfynd/A 59526-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>130162427</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>130162528</v>
       </c>
       <c r="B4" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59526-2025 artfynd.xlsx
+++ b/artfynd/A 59526-2025 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>130162528</v>
       </c>
       <c r="B4" t="n">
-        <v>58226</v>
+        <v>58234</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59526-2025 artfynd.xlsx
+++ b/artfynd/A 59526-2025 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>130162528</v>
       </c>
       <c r="B4" t="n">
-        <v>58234</v>
+        <v>58235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59526-2025 artfynd.xlsx
+++ b/artfynd/A 59526-2025 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>130162528</v>
       </c>
       <c r="B4" t="n">
-        <v>58235</v>
+        <v>58236</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59526-2025 artfynd.xlsx
+++ b/artfynd/A 59526-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>130162427</v>
       </c>
       <c r="B3" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59526-2025 artfynd.xlsx
+++ b/artfynd/A 59526-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>130162427</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
